--- a/artfynd/A 33215-2025 artfynd.xlsx
+++ b/artfynd/A 33215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110154447</v>
+        <v>114538188</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>100087</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bastulönnvägen 35, Vb</t>
+          <t>Holmön, Matsgård, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>788565.2861942679</v>
+        <v>788565</v>
       </c>
       <c r="R2" t="n">
-        <v>7087244.631522303</v>
+        <v>7087213</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +764,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>RMÖ, Pettersson D500X</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,49 +789,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Friberg</t>
+          <t>Erik Owusu-Ansah</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Friberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Erik Owusu-Ansah, Michael Schneider</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117809704</v>
+        <v>114538186</v>
       </c>
       <c r="B3" t="n">
-        <v>57560</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100108</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lundsångare</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus trochiloides</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sundevall, 1837)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,24 +838,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gammal lada vid Söråkern, Holmöarna, Vb</t>
+          <t>Holmön, Matsgård, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>788471</v>
+        <v>788565</v>
       </c>
       <c r="R3" t="n">
-        <v>7087229</v>
+        <v>7087213</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,22 +894,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>RMÖ, Pettersson D500X</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +919,266 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Hansson</t>
+          <t>Erik Owusu-Ansah</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Hansson, Åsa Strand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Erik Owusu-Ansah, Michael Schneider</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114538179</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Holmön, Matsgård, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>788565</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7087213</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Holmön</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>RMÖ, Pettersson D500X</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Owusu-Ansah, Michael Schneider</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110154447</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bastulönnvägen 35, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>788565</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7087245</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Holmön</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33215-2025 artfynd.xlsx
+++ b/artfynd/A 33215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114538188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114538186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114538179</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1179,8 +1199,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110154447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>